--- a/artfynd/A 10344-2023 artfynd.xlsx
+++ b/artfynd/A 10344-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10344-2023 artfynd.xlsx
+++ b/artfynd/A 10344-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113678537</v>
+        <v>113678524</v>
       </c>
       <c r="B2" t="n">
-        <v>80438</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494916</v>
+        <v>495018</v>
       </c>
       <c r="R2" t="n">
-        <v>6885125</v>
+        <v>6885320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113678539</v>
+        <v>113678534</v>
       </c>
       <c r="B3" t="n">
-        <v>80437</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -796,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494914</v>
+        <v>494912</v>
       </c>
       <c r="R3" t="n">
-        <v>6885126</v>
+        <v>6885234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113678515</v>
+        <v>113679927</v>
       </c>
       <c r="B4" t="n">
-        <v>80437</v>
+        <v>83222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -906,37 +906,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lill-Sännan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494936</v>
+        <v>495006</v>
       </c>
       <c r="R4" t="n">
-        <v>6885141</v>
+        <v>6885224</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,16 +974,15 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Helene Andersson</t>
@@ -1005,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113678523</v>
+        <v>113678537</v>
       </c>
       <c r="B5" t="n">
-        <v>80437</v>
+        <v>80489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1016,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494958</v>
+        <v>494916</v>
       </c>
       <c r="R5" t="n">
-        <v>6885177</v>
+        <v>6885125</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,6 +1104,2406 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113678506</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>495076</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6885058</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113678510</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>494975</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6885132</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113678519</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>494963</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6885147</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113678525</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>495016</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6885324</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113678526</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>495023</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6885298</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113678530</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>494984</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6885225</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113678531</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>494973</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6885218</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113678509</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>494981</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6885120</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113678511</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>494944</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6885129</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113678512</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>494938</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6885135</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>113678515</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>494936</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6885141</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113678516</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>494956</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6885144</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113678518</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>494960</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6885147</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113678520</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>494966</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6885141</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113678521</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>494977</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6885147</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113678522</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>494976</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6885148</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113678523</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>494958</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6885177</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113678533</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>494922</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6885236</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113678539</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>494914</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6885126</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>113678513</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>494941</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6885138</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>113682512</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>494894</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6885227</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>113678514</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80444</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-Sännan, Hls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>494942</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6885139</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ytterhogdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-10-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>

--- a/artfynd/A 10344-2023 artfynd.xlsx
+++ b/artfynd/A 10344-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -782,6 +787,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678524</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678534</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113679927</t>
         </is>
       </c>
     </row>
@@ -1108,6 +1128,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678537</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678506</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
       <c r="AY7" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678510</t>
         </is>
       </c>
     </row>
@@ -1430,6 +1465,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678519</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1540,6 +1580,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678525</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678526</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678530</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678531</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1976,6 +2036,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678509</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2080,6 +2145,11 @@
       <c r="AY14" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678511</t>
         </is>
       </c>
     </row>
@@ -2192,6 +2262,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678512</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2302,6 +2377,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678515</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2412,6 +2492,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678516</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2522,6 +2607,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678518</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2632,6 +2722,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678520</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2742,6 +2837,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678521</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2852,6 +2952,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678522</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2962,6 +3067,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678523</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3072,6 +3182,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678533</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3182,6 +3297,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678539</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3292,6 +3412,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678513</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3396,6 +3521,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113682512</t>
         </is>
       </c>
     </row>
@@ -3508,8 +3638,41 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113678514</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>